--- a/Agile_sheet.xlsx
+++ b/Agile_sheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9707" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9707" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="1" r:id="rId1"/>
@@ -331,7 +331,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="192">
   <si>
     <t>Planned Sprint</t>
   </si>
@@ -673,9 +673,6 @@
   </si>
   <si>
     <t>Studied the project workflow, structure and data integration using Google sheets</t>
-  </si>
-  <si>
-    <t>In Progress</t>
   </si>
   <si>
     <t xml:space="preserve">Learnt OOPS Concepts </t>
@@ -3983,7 +3980,7 @@
       <c r="Y5" s="35"/>
       <c r="Z5" s="35"/>
     </row>
-    <row r="6" ht="26.4" spans="1:26">
+    <row r="6" ht="15.6" spans="1:26">
       <c r="A6" s="21" t="s">
         <v>110</v>
       </c>
@@ -4006,50 +4003,50 @@
         <v>113</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="I6" s="44"/>
       <c r="J6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="N6" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="R6" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="T6" s="2" t="s">
+      <c r="U6" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="U6" s="2" t="s">
+      <c r="V6" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="V6" s="2" t="s">
+      <c r="W6" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="W6" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="X6" s="35"/>
       <c r="Y6" s="35"/>
@@ -4057,7 +4054,7 @@
     </row>
     <row r="7" ht="15.6" spans="1:26">
       <c r="A7" s="21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B7" s="29">
         <v>3</v>
@@ -4066,62 +4063,62 @@
         <v>18</v>
       </c>
       <c r="D7" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="E7" s="25" t="s">
         <v>130</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>131</v>
       </c>
       <c r="F7" s="25" t="s">
         <v>93</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H7" s="31" t="s">
         <v>95</v>
       </c>
       <c r="I7" s="44"/>
       <c r="J7" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="X7" s="35"/>
       <c r="Y7" s="35"/>
@@ -4129,7 +4126,7 @@
     </row>
     <row r="8" ht="13.8" spans="1:26">
       <c r="A8" s="33" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B8" s="29">
         <v>4</v>
@@ -4138,62 +4135,62 @@
         <v>22</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E8" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="F8" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="G8" s="27" t="s">
         <v>149</v>
-      </c>
-      <c r="G8" s="27" t="s">
-        <v>150</v>
       </c>
       <c r="H8" s="31" t="s">
         <v>95</v>
       </c>
       <c r="I8" s="44"/>
       <c r="J8" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="R8" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="S8" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="T8" s="2" t="s">
+      <c r="U8" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="U8" s="2" t="s">
+      <c r="V8" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="W8" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="X8" s="35"/>
       <c r="Y8" s="35"/>
@@ -8941,31 +8938,31 @@
   <sheetData>
     <row r="1" ht="45.75" customHeight="1" spans="1:26">
       <c r="A1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -9002,16 +8999,16 @@
         <v>12</v>
       </c>
       <c r="F2" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1" spans="1:9">
@@ -9019,7 +9016,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C3" s="3">
         <v>45938</v>
@@ -9031,16 +9028,16 @@
         <v>12</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>181</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1" spans="1:9">
@@ -9048,7 +9045,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C4" s="3">
         <v>45953</v>
@@ -9060,16 +9057,16 @@
         <v>12</v>
       </c>
       <c r="F4" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1" spans="1:9">
@@ -9077,7 +9074,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C5" s="3">
         <v>45968</v>
@@ -9089,16 +9086,16 @@
         <v>12</v>
       </c>
       <c r="F5" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>191</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1" spans="1:9">
